--- a/cases/Fault_Cases/ieee14_fault_barq.xlsx
+++ b/cases/Fault_Cases/ieee14_fault_barq.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aali27/Work/repos/emt_simulator_basic/cases/Fault_Cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5083CC3A-1196-3B4D-89F9-B4E3CC7C9384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151D28CC-CBE9-C247-8F6E-2801DCA6B004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="19960" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35680" yWindow="3920" windowWidth="19960" windowHeight="14880" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fault" sheetId="14" r:id="rId1"/>
@@ -18,21 +18,17 @@
     <sheet name="PQ" sheetId="3" r:id="rId3"/>
     <sheet name="PV" sheetId="4" r:id="rId4"/>
     <sheet name="Slack" sheetId="5" r:id="rId5"/>
-    <sheet name="Shunt" sheetId="6" r:id="rId6"/>
-    <sheet name="Line" sheetId="7" r:id="rId7"/>
-    <sheet name="Area" sheetId="8" r:id="rId8"/>
-    <sheet name="GENCLS" sheetId="9" r:id="rId9"/>
-    <sheet name="TGOV1" sheetId="10" r:id="rId10"/>
-    <sheet name="EXST1" sheetId="11" r:id="rId11"/>
-    <sheet name="ESST3A" sheetId="12" r:id="rId12"/>
-    <sheet name="BusFreq" sheetId="13" r:id="rId13"/>
+    <sheet name="Line" sheetId="7" r:id="rId6"/>
+    <sheet name="Area" sheetId="8" r:id="rId7"/>
+    <sheet name="GENCLS" sheetId="9" r:id="rId8"/>
+    <sheet name="BusFreq" sheetId="13" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="121">
   <si>
     <t>idx</t>
   </si>
@@ -196,12 +192,6 @@
     <t>fn</t>
   </si>
   <si>
-    <t>Shunt_1</t>
-  </si>
-  <si>
-    <t>Shunt_2</t>
-  </si>
-  <si>
     <t>bus1</t>
   </si>
   <si>
@@ -361,9 +351,6 @@
     <t>Tq20</t>
   </si>
   <si>
-    <t>GENROU_1</t>
-  </si>
-  <si>
     <t>GENROU_2</t>
   </si>
   <si>
@@ -374,135 +361,6 @@
   </si>
   <si>
     <t>GENROU_5</t>
-  </si>
-  <si>
-    <t>syn</t>
-  </si>
-  <si>
-    <t>Tn</t>
-  </si>
-  <si>
-    <t>wref0</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>VMAX</t>
-  </si>
-  <si>
-    <t>VMIN</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>Dt</t>
-  </si>
-  <si>
-    <t>TGOV1_1</t>
-  </si>
-  <si>
-    <t>TGOV1_2</t>
-  </si>
-  <si>
-    <t>TGOV1_3</t>
-  </si>
-  <si>
-    <t>TGOV1_4</t>
-  </si>
-  <si>
-    <t>TGOV1_5</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>VIMAX</t>
-  </si>
-  <si>
-    <t>VIMIN</t>
-  </si>
-  <si>
-    <t>TC</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
-    <t>TA</t>
-  </si>
-  <si>
-    <t>VRMAX</t>
-  </si>
-  <si>
-    <t>VRMIN</t>
-  </si>
-  <si>
-    <t>KC</t>
-  </si>
-  <si>
-    <t>KF</t>
-  </si>
-  <si>
-    <t>TF</t>
-  </si>
-  <si>
-    <t>EXST1_1</t>
-  </si>
-  <si>
-    <t>KM</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>KP</t>
-  </si>
-  <si>
-    <t>KI</t>
-  </si>
-  <si>
-    <t>VBMAX</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>VGMAX</t>
-  </si>
-  <si>
-    <t>THETAP</t>
-  </si>
-  <si>
-    <t>TM</t>
-  </si>
-  <si>
-    <t>VMMAX</t>
-  </si>
-  <si>
-    <t>VMMIN</t>
-  </si>
-  <si>
-    <t>ESST3A_2</t>
-  </si>
-  <si>
-    <t>ESST3A_3</t>
-  </si>
-  <si>
-    <t>ESST3A_4</t>
-  </si>
-  <si>
-    <t>ESST3A_5</t>
   </si>
   <si>
     <t>Tf</t>
@@ -921,16 +779,16 @@
         <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -944,921 +802,22 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="E2">
         <v>9</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>1.1000000000000001</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2">
         <v>10000000000</v>
       </c>
       <c r="I2" s="2">
         <v>10000000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>0.05</v>
-      </c>
-      <c r="I2">
-        <v>1.05</v>
-      </c>
-      <c r="J2">
-        <v>0.3</v>
-      </c>
-      <c r="K2">
-        <v>0.05</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2.1</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>0.05</v>
-      </c>
-      <c r="I3">
-        <v>1.2</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0.1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2.1</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>0.05</v>
-      </c>
-      <c r="I4">
-        <v>1.2</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0.1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2.1</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>0.05</v>
-      </c>
-      <c r="I5">
-        <v>1.05</v>
-      </c>
-      <c r="J5">
-        <v>0.3</v>
-      </c>
-      <c r="K5">
-        <v>0.05</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>2.1</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>0.05</v>
-      </c>
-      <c r="I6">
-        <v>1.05</v>
-      </c>
-      <c r="J6">
-        <v>0.3</v>
-      </c>
-      <c r="K6">
-        <v>0.05</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>2.1</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2">
-        <v>0.02</v>
-      </c>
-      <c r="G2">
-        <v>99</v>
-      </c>
-      <c r="H2">
-        <v>-99</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0.02</v>
-      </c>
-      <c r="K2">
-        <v>50</v>
-      </c>
-      <c r="L2">
-        <v>0.02</v>
-      </c>
-      <c r="M2">
-        <v>9999</v>
-      </c>
-      <c r="N2">
-        <v>-9999</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0.01</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:Z5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2">
-        <v>0.02</v>
-      </c>
-      <c r="G2">
-        <v>0.2</v>
-      </c>
-      <c r="H2">
-        <v>-0.2</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>20</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>99</v>
-      </c>
-      <c r="O2">
-        <v>-99</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>3.67</v>
-      </c>
-      <c r="R2">
-        <v>0.435</v>
-      </c>
-      <c r="S2">
-        <v>5.48</v>
-      </c>
-      <c r="T2">
-        <v>0.01</v>
-      </c>
-      <c r="U2">
-        <v>9.7999999999999997E-3</v>
-      </c>
-      <c r="V2">
-        <v>3.86</v>
-      </c>
-      <c r="W2">
-        <v>3.33</v>
-      </c>
-      <c r="X2">
-        <v>0.4</v>
-      </c>
-      <c r="Y2">
-        <v>99</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3">
-        <v>0.02</v>
-      </c>
-      <c r="G3">
-        <v>0.2</v>
-      </c>
-      <c r="H3">
-        <v>-0.2</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>99</v>
-      </c>
-      <c r="O3">
-        <v>-99</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>3.67</v>
-      </c>
-      <c r="R3">
-        <v>0.435</v>
-      </c>
-      <c r="S3">
-        <v>5.48</v>
-      </c>
-      <c r="T3">
-        <v>0.01</v>
-      </c>
-      <c r="U3">
-        <v>9.7999999999999997E-3</v>
-      </c>
-      <c r="V3">
-        <v>3.86</v>
-      </c>
-      <c r="W3">
-        <v>3.33</v>
-      </c>
-      <c r="X3">
-        <v>0.4</v>
-      </c>
-      <c r="Y3">
-        <v>99</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4">
-        <v>0.02</v>
-      </c>
-      <c r="G4">
-        <v>0.2</v>
-      </c>
-      <c r="H4">
-        <v>-0.2</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>20</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>99</v>
-      </c>
-      <c r="O4">
-        <v>-99</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>3.67</v>
-      </c>
-      <c r="R4">
-        <v>0.435</v>
-      </c>
-      <c r="S4">
-        <v>5.48</v>
-      </c>
-      <c r="T4">
-        <v>0.01</v>
-      </c>
-      <c r="U4">
-        <v>9.7999999999999997E-3</v>
-      </c>
-      <c r="V4">
-        <v>3.86</v>
-      </c>
-      <c r="W4">
-        <v>3.33</v>
-      </c>
-      <c r="X4">
-        <v>0.4</v>
-      </c>
-      <c r="Y4">
-        <v>99</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5">
-        <v>0.02</v>
-      </c>
-      <c r="G5">
-        <v>0.2</v>
-      </c>
-      <c r="H5">
-        <v>-0.2</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>20</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>99</v>
-      </c>
-      <c r="O5">
-        <v>-99</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>3.67</v>
-      </c>
-      <c r="R5">
-        <v>0.435</v>
-      </c>
-      <c r="S5">
-        <v>5.48</v>
-      </c>
-      <c r="T5">
-        <v>0.01</v>
-      </c>
-      <c r="U5">
-        <v>9.7999999999999997E-3</v>
-      </c>
-      <c r="V5">
-        <v>3.86</v>
-      </c>
-      <c r="W5">
-        <v>3.33</v>
-      </c>
-      <c r="X5">
-        <v>0.4</v>
-      </c>
-      <c r="Y5">
-        <v>99</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>0.02</v>
-      </c>
-      <c r="G2">
-        <v>0.02</v>
-      </c>
-      <c r="H2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>0.02</v>
-      </c>
-      <c r="G3">
-        <v>0.02</v>
-      </c>
-      <c r="H3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0.02</v>
-      </c>
-      <c r="G4">
-        <v>0.02</v>
-      </c>
-      <c r="H4">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3391,112 +2350,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>138</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0.19</v>
-      </c>
-      <c r="J2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3">
-        <v>14</v>
-      </c>
-      <c r="F3">
-        <v>100</v>
-      </c>
-      <c r="G3">
-        <v>138</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0.15</v>
-      </c>
-      <c r="J3">
-        <v>60</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3515,10 +2368,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -3527,16 +2380,16 @@
         <v>53</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>52</v>
@@ -3545,25 +2398,25 @@
         <v>51</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>14</v>
@@ -3645,13 +2498,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3710,13 +2563,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3775,13 +2628,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -3840,13 +2693,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -3905,13 +2758,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3970,13 +2823,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -4035,13 +2888,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -4100,13 +2953,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -4165,13 +3018,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -4230,13 +3083,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -4295,13 +3148,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -4360,13 +3213,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E14">
         <v>9</v>
@@ -4425,13 +3278,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -4490,13 +3343,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E16">
         <v>12</v>
@@ -4555,13 +3408,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -4620,13 +3473,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -4685,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -4750,13 +3603,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -4815,13 +3668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -4880,7 +3733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4910,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4924,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4932,7 +3785,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4954,10 +3807,10 @@
         <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>43</v>
@@ -4969,58 +3822,58 @@
         <v>53</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>49</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
@@ -5028,13 +3881,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -5111,13 +3964,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5194,13 +4047,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -5277,13 +4130,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>8</v>
@@ -5353,6 +4206,120 @@
       </c>
       <c r="AB5">
         <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>0.02</v>
+      </c>
+      <c r="G2">
+        <v>0.02</v>
+      </c>
+      <c r="H2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0.02</v>
+      </c>
+      <c r="G3">
+        <v>0.02</v>
+      </c>
+      <c r="H3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0.02</v>
+      </c>
+      <c r="G4">
+        <v>0.02</v>
+      </c>
+      <c r="H4">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
